--- a/data/sars/alaska/tables/Alaska_2013_Appendix2.xlsx
+++ b/data/sars/alaska/tables/Alaska_2013_Appendix2.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/evajuenglingbean/Desktop/Graduate Work/Marine Mammal Stock Assessment/2013-DONE/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/alaska/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E1EB17E0-AC2C-3148-99FA-B9F1D083B482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78F783F0-4CDA-834D-B7A1-10EF665D6EAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" xr2:uid="{504DB44F-3DAF-0F4A-9088-3703074DBC8D}"/>
   </bookViews>
   <sheets>
     <sheet name="tabula-Alaska_2013_Appendix2" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="87">
   <si>
     <t>Alaska</t>
   </si>
@@ -115,9 +128,6 @@
     <t>W. N. Pacific</t>
   </si>
   <si>
-    <t>2.6/2.0</t>
-  </si>
-  <si>
     <t>CNP - entire stock</t>
   </si>
   <si>
@@ -175,9 +185,6 @@
     <t>E. U. S.</t>
   </si>
   <si>
-    <t>63,160-_x000D_78,198</t>
-  </si>
-  <si>
     <t>W. U. S.</t>
   </si>
   <si>
@@ -187,9 +194,6 @@
     <t>2004-2006</t>
   </si>
   <si>
-    <t>61,100 (provisional)</t>
-  </si>
-  <si>
     <t>Baird's beaked whale</t>
   </si>
   <si>
@@ -278,6 +282,18 @@
   </si>
   <si>
     <t>comments</t>
+  </si>
+  <si>
+    <t>n_est_notes</t>
+  </si>
+  <si>
+    <t>provisional</t>
+  </si>
+  <si>
+    <t>63,160-78,198</t>
+  </si>
+  <si>
+    <t>pbr_notes</t>
   </si>
 </sst>
 </file>
@@ -773,10 +789,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -1154,66 +1169,71 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBD781A1-367D-9040-9401-D405AF2363B0}">
-  <dimension ref="A1:O46"/>
+  <dimension ref="A1:Q46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34.1640625" customWidth="1"/>
     <col min="2" max="2" width="29.5" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" style="2"/>
+    <col min="3" max="4" width="18.83203125" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E1" t="s">
         <v>71</v>
       </c>
-      <c r="B1" t="s">
+      <c r="F1" t="s">
         <v>72</v>
       </c>
-      <c r="C1" t="s">
+      <c r="G1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" t="s">
         <v>73</v>
       </c>
-      <c r="D1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
         <v>75</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
+        <v>76</v>
+      </c>
+      <c r="K1" t="s">
         <v>77</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H1" s="2" t="s">
+      <c r="L1" t="s">
+        <v>86</v>
+      </c>
+      <c r="M1" t="s">
         <v>78</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="N1" t="s">
         <v>79</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="O1" t="s">
         <v>80</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="P1" t="s">
         <v>81</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="Q1" t="s">
         <v>82</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B2" t="s">
         <v>0</v>
@@ -1221,32 +1241,32 @@
       <c r="C2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2">
+      <c r="F2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2">
         <v>0.04</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>0.5</v>
       </c>
-      <c r="J2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
+      <c r="K2" t="s">
+        <v>1</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
-      <c r="N2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1256,32 +1276,32 @@
       <c r="C3" t="s">
         <v>1</v>
       </c>
-      <c r="E3" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3">
+      <c r="F3" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3">
         <v>0.12</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>0.5</v>
       </c>
-      <c r="J3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3">
+      <c r="K3" t="s">
+        <v>1</v>
+      </c>
+      <c r="M3">
         <v>1.8</v>
       </c>
-      <c r="L3" s="1">
+      <c r="N3" s="1">
         <v>6788</v>
       </c>
-      <c r="M3" s="1">
+      <c r="O3" s="1">
         <v>6790</v>
       </c>
-      <c r="N3" t="s">
+      <c r="P3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1291,41 +1311,42 @@
       <c r="C4" s="1">
         <v>39258</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1"/>
+      <c r="E4">
         <v>0.23</v>
       </c>
-      <c r="E4" s="1">
+      <c r="F4" s="1">
         <v>32453</v>
       </c>
-      <c r="F4" s="1">
+      <c r="G4" s="1">
         <v>19</v>
       </c>
-      <c r="G4" s="2">
+      <c r="H4">
         <v>1992</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>0.04</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>0.5</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>7</v>
       </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
         <v>126</v>
       </c>
-      <c r="M4">
+      <c r="O4">
         <v>126</v>
       </c>
-      <c r="N4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1335,41 +1356,42 @@
       <c r="C5" s="1">
         <v>3710</v>
       </c>
-      <c r="D5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="1">
+      <c r="D5" s="1"/>
+      <c r="E5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1">
         <v>3710</v>
       </c>
-      <c r="F5" s="1">
+      <c r="G5" s="1">
         <v>12</v>
       </c>
-      <c r="G5" s="2">
+      <c r="H5">
         <v>1998</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>0.04</v>
       </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5" t="s">
         <v>7</v>
       </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
         <v>94.2</v>
       </c>
-      <c r="M5">
+      <c r="O5">
         <v>94.2</v>
       </c>
-      <c r="N5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1379,41 +1401,42 @@
       <c r="C6" s="1">
         <v>28406</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1"/>
+      <c r="E6">
         <v>0.24</v>
       </c>
-      <c r="E6" s="1">
+      <c r="F6" s="1">
         <v>20231</v>
       </c>
-      <c r="F6" s="1">
+      <c r="G6" s="1">
         <v>10</v>
       </c>
-      <c r="G6" s="2">
+      <c r="H6">
         <v>2000</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>0.04</v>
       </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6" t="s">
         <v>7</v>
       </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
         <v>192.6</v>
       </c>
-      <c r="M6">
+      <c r="O6">
         <v>192.6</v>
       </c>
-      <c r="N6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1423,44 +1446,45 @@
       <c r="C7" s="1">
         <v>2877</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1"/>
+      <c r="E7">
         <v>0.2</v>
       </c>
-      <c r="E7" s="1">
+      <c r="F7" s="1">
         <v>2467</v>
       </c>
-      <c r="F7" s="1">
+      <c r="G7" s="1">
         <v>6</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7">
         <v>2005</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>0.04</v>
       </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
       <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
         <v>49</v>
       </c>
-      <c r="K7">
+      <c r="M7">
         <v>0.8</v>
       </c>
-      <c r="L7">
+      <c r="N7">
         <v>20</v>
       </c>
-      <c r="M7">
+      <c r="O7">
         <v>20.8</v>
       </c>
-      <c r="N7" t="s">
-        <v>2</v>
-      </c>
-      <c r="O7" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -1470,42 +1494,42 @@
       <c r="C8">
         <v>312</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>0.1</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>280</v>
       </c>
-      <c r="F8" s="1">
-        <v>1</v>
-      </c>
-      <c r="G8" s="2">
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="H8">
         <v>2012</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>0.04</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>0.1</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>7</v>
       </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
       <c r="M8">
         <v>0</v>
       </c>
-      <c r="N8" t="s">
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8" t="s">
         <v>4</v>
       </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="Q8" s="2"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1515,43 +1539,44 @@
       <c r="C9" s="1">
         <v>12631</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1"/>
+      <c r="E9">
         <v>0.24</v>
       </c>
-      <c r="E9" s="1">
+      <c r="F9" s="1">
         <v>10314</v>
       </c>
-      <c r="F9" s="1">
+      <c r="G9" s="1">
         <v>8</v>
       </c>
-      <c r="G9" s="2">
+      <c r="H9">
         <v>2004</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>0.04</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>0.5</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>103</v>
       </c>
-      <c r="K9">
+      <c r="M9">
         <v>0.4</v>
       </c>
-      <c r="L9">
+      <c r="N9">
         <v>39</v>
       </c>
-      <c r="M9">
+      <c r="O9">
         <v>39.4</v>
       </c>
-      <c r="N9" t="s">
+      <c r="P9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B10" t="s">
         <v>0</v>
@@ -1559,34 +1584,34 @@
       <c r="C10" t="s">
         <v>1</v>
       </c>
-      <c r="E10" t="s">
-        <v>1</v>
-      </c>
-      <c r="H10">
+      <c r="F10" t="s">
+        <v>1</v>
+      </c>
+      <c r="I10">
         <v>0.04</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>0.5</v>
       </c>
-      <c r="J10" t="s">
-        <v>1</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
+      <c r="K10" t="s">
+        <v>1</v>
       </c>
       <c r="M10">
         <v>0</v>
       </c>
-      <c r="N10" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B11" t="s">
         <v>0</v>
@@ -1594,41 +1619,42 @@
       <c r="C11" s="1">
         <v>83400</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1"/>
+      <c r="E11">
         <v>9.7000000000000003E-2</v>
       </c>
-      <c r="E11" t="s">
-        <v>1</v>
-      </c>
-      <c r="F11" s="1">
+      <c r="F11" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
         <v>18</v>
       </c>
-      <c r="G11" s="2">
+      <c r="H11">
         <v>1993</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>0.04</v>
       </c>
-      <c r="I11">
-        <v>1</v>
-      </c>
-      <c r="J11" t="s">
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11" t="s">
         <v>7</v>
-      </c>
-      <c r="K11">
-        <v>28.9</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
       </c>
       <c r="M11">
         <v>28.9</v>
       </c>
-      <c r="N11" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>28.9</v>
+      </c>
+      <c r="P11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1638,41 +1664,41 @@
       <c r="C12" t="s">
         <v>1</v>
       </c>
-      <c r="D12" t="s">
-        <v>1</v>
-      </c>
       <c r="E12" t="s">
         <v>1</v>
       </c>
-      <c r="F12" s="1">
-        <v>2</v>
-      </c>
-      <c r="G12" s="2">
+      <c r="F12" t="s">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1">
+        <v>2</v>
+      </c>
+      <c r="H12">
         <v>2010</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>0.04</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>0.1</v>
       </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
         <v>7</v>
       </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
       <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
         <v>0.4</v>
       </c>
-      <c r="N12" t="s">
+      <c r="P12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -1682,44 +1708,45 @@
       <c r="C13" s="1">
         <v>11146</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="1"/>
+      <c r="E13">
         <v>0.24199999999999999</v>
       </c>
-      <c r="E13" s="1">
+      <c r="F13" s="1">
         <v>9116</v>
       </c>
-      <c r="F13" s="1">
+      <c r="G13" s="1">
         <v>15</v>
       </c>
-      <c r="G13" s="2">
+      <c r="H13">
         <v>1997</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>0.04</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>0.5</v>
       </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
         <v>7</v>
-      </c>
-      <c r="K13">
-        <v>22.6</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
       </c>
       <c r="M13">
         <v>22.6</v>
       </c>
-      <c r="N13" t="s">
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>22.6</v>
+      </c>
+      <c r="P13" t="s">
         <v>4</v>
       </c>
-      <c r="O13" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1729,41 +1756,42 @@
       <c r="C14" s="1">
         <v>31046</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="1"/>
+      <c r="E14">
         <v>0.214</v>
       </c>
-      <c r="E14" s="1">
+      <c r="F14" s="1">
         <v>25987</v>
       </c>
-      <c r="F14" s="1">
+      <c r="G14" s="1">
         <v>14</v>
       </c>
-      <c r="G14" s="2">
+      <c r="H14">
         <v>1998</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>0.04</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>0.5</v>
       </c>
-      <c r="J14" t="s">
+      <c r="K14" t="s">
         <v>7</v>
-      </c>
-      <c r="K14">
-        <v>71.400000000000006</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
       </c>
       <c r="M14">
         <v>71.400000000000006</v>
       </c>
-      <c r="N14" t="s">
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>71.400000000000006</v>
+      </c>
+      <c r="P14" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -1773,41 +1801,42 @@
       <c r="C15" s="1">
         <v>48215</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="1"/>
+      <c r="E15">
         <v>0.223</v>
       </c>
-      <c r="E15" s="1">
+      <c r="F15" s="1">
         <v>40039</v>
       </c>
-      <c r="F15" s="1">
+      <c r="G15" s="1">
         <v>12</v>
       </c>
-      <c r="G15" s="2">
+      <c r="H15">
         <v>1999</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>0.04</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>0.5</v>
       </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
         <v>7</v>
       </c>
-      <c r="K15">
+      <c r="M15">
         <v>0.36</v>
       </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
         <v>0.76</v>
       </c>
-      <c r="N15" t="s">
+      <c r="P15" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -1817,38 +1846,39 @@
       <c r="C16" s="1">
         <v>3579</v>
       </c>
-      <c r="E16" s="1">
+      <c r="D16" s="1"/>
+      <c r="F16" s="1">
         <v>3313</v>
       </c>
-      <c r="F16" s="1">
+      <c r="G16" s="1">
         <v>7</v>
       </c>
-      <c r="G16" s="2">
+      <c r="H16">
         <v>2004</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>0.12</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>0.5</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>99</v>
       </c>
-      <c r="K16">
-        <v>1</v>
-      </c>
-      <c r="L16">
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
         <v>90</v>
       </c>
-      <c r="M16">
+      <c r="O16">
         <v>93.1</v>
       </c>
-      <c r="N16" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P16" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -1858,38 +1888,38 @@
       <c r="C17">
         <v>232</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>232</v>
       </c>
-      <c r="F17" s="1">
-        <v>1</v>
-      </c>
-      <c r="G17" s="2">
+      <c r="G17" s="1">
+        <v>1</v>
+      </c>
+      <c r="H17">
         <v>2010</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>0.12</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>0.5</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>7</v>
       </c>
-      <c r="K17">
-        <v>1</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
       <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
         <v>3.1</v>
       </c>
-      <c r="N17" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P17" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -1899,38 +1929,40 @@
       <c r="C18" s="1">
         <v>18577</v>
       </c>
-      <c r="E18" s="1">
+      <c r="D18" s="1"/>
+      <c r="F18" s="1">
         <v>17690</v>
       </c>
-      <c r="F18" s="1">
+      <c r="G18" s="1">
         <v>6</v>
       </c>
-      <c r="G18" s="2">
+      <c r="H18">
         <v>2005</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>0.12</v>
       </c>
-      <c r="I18">
-        <v>1</v>
-      </c>
-      <c r="J18" s="1">
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18" s="1">
         <v>1061</v>
       </c>
-      <c r="K18">
-        <v>1</v>
-      </c>
-      <c r="L18">
+      <c r="L18" s="1"/>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
         <v>141</v>
       </c>
-      <c r="M18">
+      <c r="O18">
         <v>144.1</v>
       </c>
-      <c r="N18" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P18" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -1940,38 +1972,39 @@
       <c r="C19" s="1">
         <v>4509</v>
       </c>
-      <c r="E19" s="1">
+      <c r="D19" s="1"/>
+      <c r="F19" s="1">
         <v>4272</v>
       </c>
-      <c r="F19" s="1">
+      <c r="G19" s="1">
         <v>5</v>
       </c>
-      <c r="G19" s="2">
+      <c r="H19">
         <v>2006</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>0.12</v>
       </c>
-      <c r="I19">
-        <v>1</v>
-      </c>
       <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19">
         <v>256</v>
       </c>
-      <c r="K19">
-        <v>1</v>
-      </c>
-      <c r="L19">
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="N19">
         <v>131</v>
       </c>
-      <c r="M19">
+      <c r="O19">
         <v>134.1</v>
       </c>
-      <c r="N19" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P19" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -1981,79 +2014,81 @@
       <c r="C20" s="1">
         <v>11117</v>
       </c>
-      <c r="E20" s="1">
+      <c r="D20" s="1"/>
+      <c r="F20" s="1">
         <v>10645</v>
       </c>
-      <c r="F20" s="1">
+      <c r="G20" s="1">
         <v>5</v>
       </c>
-      <c r="G20" s="2">
+      <c r="H20">
         <v>2006</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>0.12</v>
       </c>
-      <c r="I20">
-        <v>1</v>
-      </c>
       <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20">
         <v>639</v>
       </c>
-      <c r="K20">
-        <v>1</v>
-      </c>
-      <c r="L20">
+      <c r="M20">
+        <v>1</v>
+      </c>
+      <c r="N20">
         <v>78</v>
       </c>
-      <c r="M20">
+      <c r="O20">
         <v>81.099999999999994</v>
       </c>
-      <c r="N20" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P20" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C21" s="1">
         <v>31503</v>
       </c>
-      <c r="E21" s="1">
+      <c r="D21" s="1"/>
+      <c r="F21" s="1">
         <v>27157</v>
       </c>
-      <c r="F21" s="1">
+      <c r="G21" s="1">
         <v>5</v>
       </c>
-      <c r="G21" s="2">
+      <c r="H21">
         <v>2006</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>0.12</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>0.5</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>815</v>
       </c>
-      <c r="K21">
+      <c r="M21">
         <v>25</v>
       </c>
-      <c r="L21">
+      <c r="N21">
         <v>439</v>
       </c>
-      <c r="M21">
+      <c r="O21">
         <v>466.1</v>
       </c>
-      <c r="N21" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -2063,79 +2098,82 @@
       <c r="C22" s="1">
         <v>22900</v>
       </c>
-      <c r="E22" s="1">
+      <c r="D22" s="1"/>
+      <c r="F22" s="1">
         <v>21896</v>
       </c>
-      <c r="F22" s="1">
+      <c r="G22" s="1">
         <v>5</v>
       </c>
-      <c r="G22" s="2">
+      <c r="H22">
         <v>2006</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>0.12</v>
       </c>
-      <c r="I22">
-        <v>1</v>
-      </c>
-      <c r="J22" s="1">
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22" s="1">
         <v>1314</v>
       </c>
-      <c r="K22">
-        <v>1</v>
-      </c>
-      <c r="L22">
+      <c r="L22" s="1"/>
+      <c r="M22">
+        <v>1</v>
+      </c>
+      <c r="N22">
         <v>233</v>
       </c>
-      <c r="M22">
+      <c r="O22">
         <v>236.1</v>
       </c>
-      <c r="N22" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P22" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C23" s="1">
         <v>5042</v>
       </c>
-      <c r="E23" s="1">
+      <c r="D23" s="1"/>
+      <c r="F23" s="1">
         <v>4735</v>
       </c>
-      <c r="F23" s="1">
+      <c r="G23" s="1">
         <v>4</v>
       </c>
-      <c r="G23" s="2">
+      <c r="H23">
         <v>2007</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>0.12</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>0.5</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>142</v>
       </c>
-      <c r="K23">
-        <v>1</v>
-      </c>
-      <c r="L23">
+      <c r="M23">
+        <v>1</v>
+      </c>
+      <c r="N23">
         <v>52</v>
       </c>
-      <c r="M23">
+      <c r="O23">
         <v>55.1</v>
       </c>
-      <c r="N23" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P23" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>20</v>
       </c>
@@ -2145,38 +2183,39 @@
       <c r="C24" s="1">
         <v>8870</v>
       </c>
-      <c r="E24" s="1">
+      <c r="D24" s="1"/>
+      <c r="F24" s="1">
         <v>8481</v>
       </c>
-      <c r="F24" s="1">
+      <c r="G24" s="1">
         <v>4</v>
       </c>
-      <c r="G24" s="2">
+      <c r="H24">
         <v>2007</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>0.12</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <v>0.5</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>254</v>
       </c>
-      <c r="K24">
-        <v>1</v>
-      </c>
-      <c r="L24">
+      <c r="M24">
+        <v>1</v>
+      </c>
+      <c r="N24">
         <v>30</v>
       </c>
-      <c r="M24">
+      <c r="O24">
         <v>33.1</v>
       </c>
-      <c r="N24" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P24" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>20</v>
       </c>
@@ -2186,79 +2225,81 @@
       <c r="C25" s="1">
         <v>8586</v>
       </c>
-      <c r="E25" s="1">
+      <c r="D25" s="1"/>
+      <c r="F25" s="1">
         <v>8222</v>
       </c>
-      <c r="F25" s="1">
+      <c r="G25" s="1">
         <v>4</v>
       </c>
-      <c r="G25" s="2">
+      <c r="H25">
         <v>2007</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <v>0.12</v>
       </c>
-      <c r="I25">
+      <c r="J25">
         <v>0.5</v>
       </c>
-      <c r="J25">
+      <c r="K25">
         <v>247</v>
       </c>
-      <c r="K25">
-        <v>1</v>
-      </c>
-      <c r="L25">
+      <c r="M25">
+        <v>1</v>
+      </c>
+      <c r="N25">
         <v>222</v>
       </c>
-      <c r="M25">
+      <c r="O25">
         <v>225.1</v>
       </c>
-      <c r="N25" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P25" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>20</v>
       </c>
       <c r="B26" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C26" s="1">
         <v>14388</v>
       </c>
-      <c r="E26" s="1">
+      <c r="D26" s="1"/>
+      <c r="F26" s="1">
         <v>13682</v>
       </c>
-      <c r="F26" s="1">
+      <c r="G26" s="1">
         <v>5</v>
       </c>
-      <c r="G26" s="2">
+      <c r="H26">
         <v>2003</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>0.12</v>
       </c>
-      <c r="I26">
-        <v>1</v>
-      </c>
       <c r="J26">
+        <v>1</v>
+      </c>
+      <c r="K26">
         <v>821</v>
       </c>
-      <c r="K26">
-        <v>1</v>
-      </c>
-      <c r="L26">
+      <c r="M26">
+        <v>1</v>
+      </c>
+      <c r="N26">
         <v>157</v>
       </c>
-      <c r="M26">
+      <c r="O26">
         <v>160.1</v>
       </c>
-      <c r="N26" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P26" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>20</v>
       </c>
@@ -2268,38 +2309,40 @@
       <c r="C27" s="1">
         <v>23289</v>
       </c>
-      <c r="E27" s="1">
+      <c r="D27" s="1"/>
+      <c r="F27" s="1">
         <v>22471</v>
       </c>
-      <c r="F27" s="1">
+      <c r="G27" s="1">
         <v>5</v>
       </c>
-      <c r="G27" s="2">
+      <c r="H27">
         <v>2003</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <v>0.12</v>
       </c>
-      <c r="I27">
-        <v>1</v>
-      </c>
-      <c r="J27" s="1">
+      <c r="J27">
+        <v>1</v>
+      </c>
+      <c r="K27" s="1">
         <v>1348</v>
       </c>
-      <c r="K27">
-        <v>1</v>
-      </c>
-      <c r="L27">
+      <c r="L27" s="1"/>
+      <c r="M27">
+        <v>1</v>
+      </c>
+      <c r="N27">
         <v>164</v>
       </c>
-      <c r="M27">
+      <c r="O27">
         <v>167.1</v>
       </c>
-      <c r="N27" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P27" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>29</v>
       </c>
@@ -2309,784 +2352,801 @@
       <c r="C28">
         <v>938</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>0.3</v>
       </c>
-      <c r="E28">
+      <c r="F28">
         <v>732</v>
       </c>
-      <c r="F28" s="1">
+      <c r="G28" s="1">
         <v>6</v>
       </c>
-      <c r="G28" s="2">
+      <c r="H28">
         <v>2006</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <v>0.1</v>
       </c>
-      <c r="J28" t="s">
-        <v>31</v>
-      </c>
       <c r="K28">
+        <v>2.6</v>
+      </c>
+      <c r="L28">
+        <v>2</v>
+      </c>
+      <c r="M28">
         <v>0.4</v>
       </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28">
-        <v>2</v>
-      </c>
-      <c r="N28" t="s">
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>2</v>
+      </c>
+      <c r="P28" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29" s="1">
         <v>7469</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="1"/>
+      <c r="E29">
         <v>0.3</v>
       </c>
-      <c r="E29" s="1">
+      <c r="F29" s="1">
         <v>5833</v>
       </c>
-      <c r="F29" s="1">
+      <c r="G29" s="1">
         <v>6</v>
       </c>
-      <c r="G29" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H29">
+      <c r="H29" t="s">
+        <v>52</v>
+      </c>
+      <c r="I29">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="I29">
+      <c r="J29">
         <v>0.3</v>
       </c>
-      <c r="J29">
+      <c r="K29">
         <v>61.2</v>
       </c>
-      <c r="K29">
+      <c r="M29">
         <v>7.45</v>
       </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29">
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
         <v>13.9</v>
       </c>
-      <c r="N29" t="s">
+      <c r="P29" t="s">
         <v>4</v>
       </c>
-      <c r="O29" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" t="s">
         <v>33</v>
-      </c>
-      <c r="B30" t="s">
-        <v>34</v>
       </c>
       <c r="C30" s="1">
         <v>2347</v>
       </c>
-      <c r="D30" t="s">
-        <v>1</v>
-      </c>
-      <c r="E30" s="1">
+      <c r="D30" s="1"/>
+      <c r="E30" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="1">
         <v>2347</v>
       </c>
-      <c r="F30" s="1">
-        <v>1</v>
-      </c>
-      <c r="G30" s="2">
+      <c r="G30" s="1">
+        <v>1</v>
+      </c>
+      <c r="H30">
         <v>2012</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <v>0.04</v>
       </c>
-      <c r="I30">
+      <c r="J30">
         <v>0.5</v>
       </c>
-      <c r="J30">
+      <c r="K30">
         <v>23.4</v>
-      </c>
-      <c r="K30">
-        <v>0.9</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
       </c>
       <c r="M30">
         <v>0.9</v>
       </c>
-      <c r="N30" t="s">
-        <v>2</v>
-      </c>
-      <c r="O30" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0.9</v>
+      </c>
+      <c r="P30" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q30" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C31">
         <v>261</v>
       </c>
-      <c r="D31" t="s">
-        <v>1</v>
-      </c>
-      <c r="E31">
+      <c r="E31" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31">
         <v>261</v>
       </c>
-      <c r="F31" s="1">
-        <v>2</v>
-      </c>
-      <c r="G31" s="2">
+      <c r="G31" s="1">
+        <v>2</v>
+      </c>
+      <c r="H31">
         <v>2011</v>
       </c>
-      <c r="H31">
+      <c r="I31">
         <v>0.03</v>
       </c>
-      <c r="I31">
+      <c r="J31">
         <v>0.5</v>
       </c>
-      <c r="J31">
+      <c r="K31">
         <v>1.96</v>
       </c>
-      <c r="K31">
-        <v>0</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
       <c r="M31">
         <v>0</v>
       </c>
-      <c r="N31" t="s">
-        <v>2</v>
-      </c>
-      <c r="O31" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q31" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32">
         <v>7</v>
       </c>
-      <c r="D32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E32">
+      <c r="E32" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32">
         <v>7</v>
       </c>
-      <c r="F32" s="1">
-        <v>1</v>
-      </c>
-      <c r="G32" s="2">
+      <c r="G32" s="1">
+        <v>1</v>
+      </c>
+      <c r="H32">
         <v>2012</v>
       </c>
-      <c r="H32">
+      <c r="I32">
         <v>0.04</v>
       </c>
-      <c r="I32">
+      <c r="J32">
         <v>0.1</v>
       </c>
-      <c r="J32">
-        <v>0</v>
-      </c>
       <c r="K32">
         <v>0</v>
       </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
       <c r="M32">
         <v>0</v>
       </c>
-      <c r="N32" t="s">
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32" t="s">
         <v>4</v>
       </c>
-      <c r="O32" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C33">
         <v>587</v>
       </c>
-      <c r="D33" t="s">
-        <v>1</v>
-      </c>
-      <c r="E33">
+      <c r="E33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33">
         <v>587</v>
       </c>
-      <c r="F33" s="1">
-        <v>1</v>
-      </c>
-      <c r="G33" s="2">
+      <c r="G33" s="1">
+        <v>1</v>
+      </c>
+      <c r="H33">
         <v>2012</v>
       </c>
-      <c r="H33">
+      <c r="I33">
         <v>0.04</v>
       </c>
-      <c r="I33">
+      <c r="J33">
         <v>0.5</v>
       </c>
-      <c r="J33">
+      <c r="K33">
         <v>5.9</v>
-      </c>
-      <c r="K33">
-        <v>0.6</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
       </c>
       <c r="M33">
         <v>0.6</v>
       </c>
-      <c r="N33" t="s">
-        <v>2</v>
-      </c>
-      <c r="O33" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0.6</v>
+      </c>
+      <c r="P33" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C34">
         <v>243</v>
       </c>
-      <c r="D34" t="s">
-        <v>1</v>
-      </c>
-      <c r="E34">
+      <c r="E34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34">
         <v>243</v>
       </c>
-      <c r="F34" s="1">
+      <c r="G34" s="1">
         <v>3</v>
       </c>
-      <c r="G34" s="2">
+      <c r="H34">
         <v>2009</v>
       </c>
-      <c r="H34">
+      <c r="I34">
         <v>0.04</v>
       </c>
-      <c r="I34">
+      <c r="J34">
         <v>0.5</v>
       </c>
-      <c r="J34">
+      <c r="K34">
         <v>2.4</v>
       </c>
-      <c r="K34">
-        <v>0</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
       <c r="M34">
         <v>0</v>
       </c>
-      <c r="N34" t="s">
-        <v>2</v>
-      </c>
-      <c r="O34" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q34" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" t="s">
+        <v>0</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" t="s">
+        <v>1</v>
+      </c>
+      <c r="I35">
+        <v>0.04</v>
+      </c>
+      <c r="J35">
+        <v>0.5</v>
+      </c>
+      <c r="K35" t="s">
+        <v>1</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0.2</v>
+      </c>
+      <c r="P35" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
         <v>36</v>
       </c>
-      <c r="B35" t="s">
-        <v>0</v>
-      </c>
-      <c r="C35" t="s">
-        <v>1</v>
-      </c>
-      <c r="E35" t="s">
-        <v>1</v>
-      </c>
-      <c r="H35">
+      <c r="B36" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" t="s">
+        <v>1</v>
+      </c>
+      <c r="I36">
         <v>0.04</v>
       </c>
-      <c r="I35">
+      <c r="J36">
         <v>0.5</v>
       </c>
-      <c r="J35" t="s">
-        <v>1</v>
-      </c>
-      <c r="K35">
-        <v>0</v>
-      </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35">
-        <v>0.2</v>
-      </c>
-      <c r="N35" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" t="s">
+      <c r="K36" t="s">
+        <v>1</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
         <v>38</v>
       </c>
-      <c r="C36" t="s">
-        <v>1</v>
-      </c>
-      <c r="E36" t="s">
-        <v>1</v>
-      </c>
-      <c r="H36">
-        <v>0.04</v>
-      </c>
-      <c r="I36">
-        <v>0.5</v>
-      </c>
-      <c r="J36" t="s">
-        <v>1</v>
-      </c>
-      <c r="K36">
-        <v>0</v>
-      </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-      <c r="M36">
-        <v>0</v>
-      </c>
-      <c r="N36" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
+      <c r="B37" t="s">
         <v>39</v>
-      </c>
-      <c r="B37" t="s">
-        <v>40</v>
       </c>
       <c r="C37" s="1">
         <v>639545</v>
       </c>
-      <c r="D37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E37" s="1">
+      <c r="D37" s="1"/>
+      <c r="E37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="1">
         <v>541317</v>
       </c>
-      <c r="F37" s="1">
-        <v>1</v>
-      </c>
-      <c r="G37" s="2">
+      <c r="G37" s="1">
+        <v>1</v>
+      </c>
+      <c r="H37">
         <v>2011</v>
       </c>
-      <c r="H37">
+      <c r="I37">
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="I37">
+      <c r="J37">
         <v>0.5</v>
       </c>
-      <c r="J37" s="1">
+      <c r="K37" s="1">
         <v>11638</v>
       </c>
-      <c r="K37">
+      <c r="L37" s="1"/>
+      <c r="M37">
         <v>4.5999999999999996</v>
       </c>
-      <c r="L37">
+      <c r="N37">
         <v>463</v>
       </c>
-      <c r="M37">
+      <c r="O37">
         <v>471</v>
       </c>
-      <c r="N37" t="s">
+      <c r="P37" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C38" s="1">
         <v>26880</v>
       </c>
-      <c r="D38" t="s">
-        <v>1</v>
-      </c>
+      <c r="D38" s="1"/>
       <c r="E38" t="s">
         <v>1</v>
       </c>
       <c r="F38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G38" s="2">
+        <v>1</v>
+      </c>
+      <c r="G38" t="s">
+        <v>51</v>
+      </c>
+      <c r="H38">
         <v>1990</v>
       </c>
-      <c r="H38">
+      <c r="I38">
         <v>0.04</v>
       </c>
-      <c r="I38">
+      <c r="J38">
         <v>0.5</v>
       </c>
-      <c r="J38" t="s">
+      <c r="K38" t="s">
         <v>7</v>
       </c>
-      <c r="K38">
-        <v>0</v>
-      </c>
-      <c r="L38">
-        <v>0</v>
-      </c>
       <c r="M38">
         <v>0</v>
       </c>
-      <c r="N38" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="1">
+        <v>61100</v>
+      </c>
+      <c r="D39" t="s">
+        <v>84</v>
+      </c>
+      <c r="F39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+      <c r="H39">
+        <v>2012</v>
+      </c>
+      <c r="I39">
+        <v>0.12</v>
+      </c>
+      <c r="J39">
+        <v>0.5</v>
+      </c>
+      <c r="K39" t="s">
+        <v>1</v>
+      </c>
+      <c r="M39">
+        <v>1.02</v>
+      </c>
+      <c r="N39">
+        <v>193</v>
+      </c>
+      <c r="O39">
+        <v>194</v>
+      </c>
+      <c r="P39" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
         <v>42</v>
       </c>
-      <c r="B39" t="s">
-        <v>0</v>
-      </c>
-      <c r="C39" t="s">
-        <v>55</v>
-      </c>
-      <c r="E39" t="s">
-        <v>1</v>
-      </c>
-      <c r="F39">
-        <v>1</v>
-      </c>
-      <c r="G39" s="2">
-        <v>2012</v>
-      </c>
-      <c r="H39">
-        <v>0.12</v>
-      </c>
-      <c r="I39">
-        <v>0.5</v>
-      </c>
-      <c r="J39" t="s">
-        <v>1</v>
-      </c>
-      <c r="K39">
-        <v>1.02</v>
-      </c>
-      <c r="L39">
-        <v>193</v>
-      </c>
-      <c r="M39">
-        <v>194</v>
-      </c>
-      <c r="N39" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
+      <c r="B40" t="s">
         <v>43</v>
-      </c>
-      <c r="B40" t="s">
-        <v>44</v>
       </c>
       <c r="C40">
         <v>31</v>
       </c>
-      <c r="D40">
+      <c r="E40">
         <v>0.23</v>
       </c>
-      <c r="E40">
+      <c r="F40">
         <v>25.7</v>
       </c>
-      <c r="G40" s="2">
+      <c r="H40">
         <v>2010</v>
       </c>
-      <c r="H40">
+      <c r="I40">
         <v>0.04</v>
       </c>
-      <c r="I40">
+      <c r="J40">
         <v>0.1</v>
       </c>
-      <c r="J40">
-        <v>0</v>
-      </c>
       <c r="K40">
         <v>0</v>
       </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
       <c r="M40">
         <v>0</v>
       </c>
-      <c r="N40" t="s">
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" t="s">
+        <v>0</v>
+      </c>
+      <c r="C41" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" t="s">
+        <v>1</v>
+      </c>
+      <c r="I41">
+        <v>0.12</v>
+      </c>
+      <c r="J41">
+        <v>0.5</v>
+      </c>
+      <c r="K41" t="s">
+        <v>1</v>
+      </c>
+      <c r="M41">
+        <v>3.52</v>
+      </c>
+      <c r="N41" s="1">
+        <v>9567</v>
+      </c>
+      <c r="O41" s="1">
+        <v>9571</v>
+      </c>
+      <c r="P41" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
         <v>45</v>
       </c>
-      <c r="B41" t="s">
-        <v>0</v>
-      </c>
-      <c r="C41" t="s">
-        <v>1</v>
-      </c>
-      <c r="E41" t="s">
-        <v>1</v>
-      </c>
-      <c r="H41">
-        <v>0.12</v>
-      </c>
-      <c r="I41">
-        <v>0.5</v>
-      </c>
-      <c r="J41" t="s">
-        <v>1</v>
-      </c>
-      <c r="K41">
-        <v>3.52</v>
-      </c>
-      <c r="L41" s="1">
-        <v>9567</v>
-      </c>
-      <c r="M41" s="1">
-        <v>9571</v>
-      </c>
-      <c r="N41" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
+      <c r="B42" t="s">
         <v>46</v>
       </c>
-      <c r="B42" t="s">
-        <v>47</v>
-      </c>
       <c r="C42" t="s">
         <v>1</v>
       </c>
-      <c r="E42" t="s">
-        <v>1</v>
-      </c>
-      <c r="H42">
+      <c r="F42" t="s">
+        <v>1</v>
+      </c>
+      <c r="I42">
         <v>0.04</v>
       </c>
-      <c r="I42">
+      <c r="J42">
         <v>0.1</v>
       </c>
-      <c r="J42" t="s">
-        <v>1</v>
-      </c>
-      <c r="K42">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="L42">
-        <v>0</v>
+      <c r="K42" t="s">
+        <v>1</v>
       </c>
       <c r="M42">
         <v>0.28000000000000003</v>
       </c>
-      <c r="N42" t="s">
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="P42" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
+        <v>47</v>
+      </c>
+      <c r="B43" t="s">
+        <v>0</v>
+      </c>
+      <c r="C43" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" t="s">
+        <v>1</v>
+      </c>
+      <c r="I43">
+        <v>0.12</v>
+      </c>
+      <c r="J43">
+        <v>0.5</v>
+      </c>
+      <c r="K43" t="s">
+        <v>1</v>
+      </c>
+      <c r="M43">
+        <v>1</v>
+      </c>
+      <c r="N43" s="1">
+        <v>5265</v>
+      </c>
+      <c r="O43" s="1">
+        <v>5266</v>
+      </c>
+      <c r="P43" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>57</v>
+      </c>
+      <c r="B44" t="s">
+        <v>0</v>
+      </c>
+      <c r="C44" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" t="s">
+        <v>1</v>
+      </c>
+      <c r="I44">
+        <v>0.04</v>
+      </c>
+      <c r="J44">
+        <v>0.5</v>
+      </c>
+      <c r="K44" t="s">
+        <v>1</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
         <v>48</v>
       </c>
-      <c r="B43" t="s">
-        <v>0</v>
-      </c>
-      <c r="C43" t="s">
-        <v>1</v>
-      </c>
-      <c r="E43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H43">
+      <c r="B45" t="s">
+        <v>49</v>
+      </c>
+      <c r="C45">
+        <f>AVERAGE(63160, 78198)</f>
+        <v>70679</v>
+      </c>
+      <c r="D45" t="s">
+        <v>85</v>
+      </c>
+      <c r="F45" s="1">
+        <v>34485</v>
+      </c>
+      <c r="G45" s="1">
+        <v>2</v>
+      </c>
+      <c r="H45">
+        <v>2011</v>
+      </c>
+      <c r="I45">
         <v>0.12</v>
       </c>
-      <c r="I43">
-        <v>0.5</v>
-      </c>
-      <c r="J43" t="s">
-        <v>1</v>
-      </c>
-      <c r="K43">
-        <v>1</v>
-      </c>
-      <c r="L43" s="1">
-        <v>5265</v>
-      </c>
-      <c r="M43" s="1">
-        <v>5266</v>
-      </c>
-      <c r="N43" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>60</v>
-      </c>
-      <c r="B44" t="s">
-        <v>0</v>
-      </c>
-      <c r="C44" t="s">
-        <v>1</v>
-      </c>
-      <c r="E44" t="s">
-        <v>1</v>
-      </c>
-      <c r="H44">
-        <v>0.04</v>
-      </c>
-      <c r="I44">
-        <v>0.5</v>
-      </c>
-      <c r="J44" t="s">
-        <v>1</v>
-      </c>
-      <c r="K44">
-        <v>0</v>
-      </c>
-      <c r="L44">
-        <v>0</v>
-      </c>
-      <c r="M44">
-        <v>0</v>
-      </c>
-      <c r="N44" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
+      <c r="J45">
+        <v>0.75</v>
+      </c>
+      <c r="K45" s="1">
+        <v>1552</v>
+      </c>
+      <c r="L45" s="1"/>
+      <c r="M45">
         <v>49</v>
       </c>
-      <c r="B45" t="s">
+      <c r="N45">
+        <v>11.9</v>
+      </c>
+      <c r="O45">
+        <v>65.099999999999994</v>
+      </c>
+      <c r="P45" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>48</v>
+      </c>
+      <c r="B46" t="s">
         <v>50</v>
-      </c>
-      <c r="C45" t="s">
-        <v>51</v>
-      </c>
-      <c r="E45" s="1">
-        <v>34485</v>
-      </c>
-      <c r="F45" s="1">
-        <v>2</v>
-      </c>
-      <c r="G45" s="2">
-        <v>2011</v>
-      </c>
-      <c r="H45">
-        <v>0.12</v>
-      </c>
-      <c r="I45">
-        <v>0.75</v>
-      </c>
-      <c r="J45" s="1">
-        <v>1552</v>
-      </c>
-      <c r="K45">
-        <v>49</v>
-      </c>
-      <c r="L45">
-        <v>11.9</v>
-      </c>
-      <c r="M45">
-        <v>65.099999999999994</v>
-      </c>
-      <c r="N45" t="s">
-        <v>4</v>
-      </c>
-      <c r="O45" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>49</v>
-      </c>
-      <c r="B46" t="s">
-        <v>52</v>
       </c>
       <c r="C46" s="1">
         <v>45659</v>
       </c>
-      <c r="E46" s="1">
+      <c r="D46" s="1"/>
+      <c r="F46" s="1">
         <v>45659</v>
       </c>
-      <c r="F46" s="1">
-        <v>1</v>
-      </c>
-      <c r="G46" s="2">
+      <c r="G46" s="1">
+        <v>1</v>
+      </c>
+      <c r="H46">
         <v>2012</v>
       </c>
-      <c r="H46">
+      <c r="I46">
         <v>0.12</v>
       </c>
-      <c r="I46">
+      <c r="J46">
         <v>0.1</v>
       </c>
-      <c r="J46">
+      <c r="K46">
         <v>274</v>
       </c>
-      <c r="K46">
+      <c r="M46">
         <v>29.6</v>
       </c>
-      <c r="L46">
+      <c r="N46">
         <v>199</v>
       </c>
-      <c r="M46">
+      <c r="O46">
         <v>230</v>
       </c>
-      <c r="N46" t="s">
+      <c r="P46" t="s">
         <v>4</v>
       </c>
     </row>

--- a/data/sars/alaska/tables/Alaska_2013_Appendix2.xlsx
+++ b/data/sars/alaska/tables/Alaska_2013_Appendix2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/alaska/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78F783F0-4CDA-834D-B7A1-10EF665D6EAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60FCD9DA-AF0B-B549-88C8-200FDAB928EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" xr2:uid="{504DB44F-3DAF-0F4A-9088-3703074DBC8D}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="89">
   <si>
     <t>Alaska</t>
   </si>
@@ -294,6 +294,12 @@
   </si>
   <si>
     <t>pbr_notes</t>
+  </si>
+  <si>
+    <t>revised_yn</t>
+  </si>
+  <si>
+    <t>yes</t>
   </si>
 </sst>
 </file>
@@ -448,7 +454,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -626,6 +632,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -789,11 +801,14 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1169,7 +1184,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBD781A1-367D-9040-9401-D405AF2363B0}">
-  <dimension ref="A1:Q46"/>
+  <dimension ref="A1:R46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34.1640625" customWidth="1"/>
@@ -1178,7 +1193,7 @@
     <col min="7" max="7" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>68</v>
       </c>
@@ -1228,80 +1243,89 @@
         <v>81</v>
       </c>
       <c r="Q1" t="s">
+        <v>87</v>
+      </c>
+      <c r="R1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2">
+      <c r="B2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="3">
         <v>0.04</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="3">
         <v>0.5</v>
       </c>
-      <c r="K2" t="s">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="K2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="3">
+        <v>0</v>
+      </c>
+      <c r="N2" s="3">
+        <v>0</v>
+      </c>
+      <c r="O2" s="3">
+        <v>0</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3">
+      <c r="B3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="3">
         <v>0.12</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="3">
         <v>0.5</v>
       </c>
-      <c r="K3" t="s">
-        <v>1</v>
-      </c>
-      <c r="M3">
+      <c r="K3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="M3" s="3">
         <v>1.8</v>
       </c>
-      <c r="N3" s="1">
+      <c r="N3" s="4">
         <v>6788</v>
       </c>
-      <c r="O3" s="1">
+      <c r="O3" s="4">
         <v>6790</v>
       </c>
-      <c r="P3" t="s">
+      <c r="P3" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q3" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1346,7 +1370,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1391,7 +1415,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1436,7 +1460,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1480,136 +1504,145 @@
       <c r="P7" t="s">
         <v>2</v>
       </c>
-      <c r="Q7" s="3" t="s">
+      <c r="R7" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+    <row r="8" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="3">
         <v>312</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="3">
         <v>0.1</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="3">
         <v>280</v>
       </c>
-      <c r="G8" s="1">
-        <v>1</v>
-      </c>
-      <c r="H8">
+      <c r="G8" s="4">
+        <v>1</v>
+      </c>
+      <c r="H8" s="3">
         <v>2012</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="3">
         <v>0.04</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="3">
         <v>0.1</v>
       </c>
-      <c r="K8" t="s">
+      <c r="K8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8" t="s">
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q8" s="2"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="Q8" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="R8" s="5"/>
+    </row>
+    <row r="9" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="4">
         <v>12631</v>
       </c>
-      <c r="D9" s="1"/>
-      <c r="E9">
+      <c r="D9" s="4"/>
+      <c r="E9" s="3">
         <v>0.24</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="4">
         <v>10314</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="4">
         <v>8</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="3">
         <v>2004</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="3">
         <v>0.04</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="3">
         <v>0.5</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="3">
         <v>103</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="3">
         <v>0.4</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="3">
         <v>39</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="3">
         <v>39.4</v>
       </c>
-      <c r="P9" t="s">
+      <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="Q9" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C10" t="s">
-        <v>1</v>
-      </c>
-      <c r="F10" t="s">
-        <v>1</v>
-      </c>
-      <c r="I10">
+      <c r="B10" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="I10" s="3">
         <v>0.04</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="3">
         <v>0.5</v>
       </c>
-      <c r="K10" t="s">
-        <v>1</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="M10" s="3">
+        <v>0</v>
+      </c>
+      <c r="N10" s="3">
+        <v>0</v>
+      </c>
+      <c r="O10" s="3">
+        <v>0</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -1654,189 +1687,201 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+    <row r="12" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C12" t="s">
-        <v>1</v>
-      </c>
-      <c r="E12" t="s">
-        <v>1</v>
-      </c>
-      <c r="F12" t="s">
-        <v>1</v>
-      </c>
-      <c r="G12" s="1">
-        <v>2</v>
-      </c>
-      <c r="H12">
+      <c r="C12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G12" s="4">
+        <v>2</v>
+      </c>
+      <c r="H12" s="3">
         <v>2010</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="3">
         <v>0.04</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="3">
         <v>0.1</v>
       </c>
-      <c r="K12" t="s">
+      <c r="K12" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
+      <c r="M12" s="3">
+        <v>0</v>
+      </c>
+      <c r="N12" s="3">
+        <v>0</v>
+      </c>
+      <c r="O12" s="3">
         <v>0.4</v>
       </c>
-      <c r="P12" t="s">
+      <c r="P12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+      <c r="Q12" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="4">
         <v>11146</v>
       </c>
-      <c r="D13" s="1"/>
-      <c r="E13">
+      <c r="D13" s="4"/>
+      <c r="E13" s="3">
         <v>0.24199999999999999</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="4">
         <v>9116</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" s="4">
         <v>15</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="3">
         <v>1997</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="3">
         <v>0.04</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="3">
         <v>0.5</v>
       </c>
-      <c r="K13" t="s">
+      <c r="K13" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="3">
         <v>22.6</v>
       </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
         <v>22.6</v>
       </c>
-      <c r="P13" t="s">
+      <c r="P13" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q13" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="R13" s="6" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+    <row r="14" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="4">
         <v>31046</v>
       </c>
-      <c r="D14" s="1"/>
-      <c r="E14">
+      <c r="D14" s="4"/>
+      <c r="E14" s="3">
         <v>0.214</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14" s="4">
         <v>25987</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" s="4">
         <v>14</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="3">
         <v>1998</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="3">
         <v>0.04</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="3">
         <v>0.5</v>
       </c>
-      <c r="K14" t="s">
+      <c r="K14" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="3">
         <v>71.400000000000006</v>
       </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>71.400000000000006</v>
       </c>
-      <c r="P14" t="s">
+      <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+      <c r="Q14" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="4">
         <v>48215</v>
       </c>
-      <c r="D15" s="1"/>
-      <c r="E15">
+      <c r="D15" s="4"/>
+      <c r="E15" s="3">
         <v>0.223</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15" s="4">
         <v>40039</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" s="4">
         <v>12</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="3">
         <v>1999</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="3">
         <v>0.04</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="3">
         <v>0.5</v>
       </c>
-      <c r="K15" t="s">
+      <c r="K15" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="3">
         <v>0.36</v>
       </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
         <v>0.76</v>
       </c>
-      <c r="P15" t="s">
+      <c r="P15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -1878,7 +1923,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -1919,7 +1964,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -1962,7 +2007,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -2004,7 +2049,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -2046,7 +2091,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -2088,7 +2133,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -2131,7 +2176,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>20</v>
       </c>
@@ -2173,7 +2218,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>20</v>
       </c>
@@ -2215,7 +2260,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>20</v>
       </c>
@@ -2257,7 +2302,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>20</v>
       </c>
@@ -2299,7 +2344,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>20</v>
       </c>
@@ -2342,338 +2387,359 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
+    <row r="28" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="3">
         <v>938</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="3">
         <v>0.3</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="3">
         <v>732</v>
       </c>
-      <c r="G28" s="1">
+      <c r="G28" s="4">
         <v>6</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="3">
         <v>2006</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="3">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="J28">
+      <c r="J28" s="3">
         <v>0.1</v>
       </c>
-      <c r="K28">
+      <c r="K28" s="3">
         <v>2.6</v>
       </c>
-      <c r="L28">
-        <v>2</v>
-      </c>
-      <c r="M28">
+      <c r="L28" s="3">
+        <v>2</v>
+      </c>
+      <c r="M28" s="3">
         <v>0.4</v>
       </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
-      <c r="O28">
-        <v>2</v>
-      </c>
-      <c r="P28" t="s">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>2</v>
+      </c>
+      <c r="P28" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
+      <c r="Q28" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C29" s="4">
         <v>7469</v>
       </c>
-      <c r="D29" s="1"/>
-      <c r="E29">
+      <c r="D29" s="4"/>
+      <c r="E29" s="3">
         <v>0.3</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F29" s="4">
         <v>5833</v>
       </c>
-      <c r="G29" s="1">
+      <c r="G29" s="4">
         <v>6</v>
       </c>
-      <c r="H29" t="s">
+      <c r="H29" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="3">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="J29">
+      <c r="J29" s="3">
         <v>0.3</v>
       </c>
-      <c r="K29">
+      <c r="K29" s="3">
         <v>61.2</v>
       </c>
-      <c r="M29">
+      <c r="M29" s="3">
         <v>7.45</v>
       </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
-      <c r="O29">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>13.9</v>
       </c>
-      <c r="P29" t="s">
+      <c r="P29" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q29" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="R29" s="6" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
+    <row r="30" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C30" s="4">
         <v>2347</v>
       </c>
-      <c r="D30" s="1"/>
-      <c r="E30" t="s">
-        <v>1</v>
-      </c>
-      <c r="F30" s="1">
+      <c r="D30" s="4"/>
+      <c r="E30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="4">
         <v>2347</v>
       </c>
-      <c r="G30" s="1">
-        <v>1</v>
-      </c>
-      <c r="H30">
+      <c r="G30" s="4">
+        <v>1</v>
+      </c>
+      <c r="H30" s="3">
         <v>2012</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="3">
         <v>0.04</v>
       </c>
-      <c r="J30">
+      <c r="J30" s="3">
         <v>0.5</v>
       </c>
-      <c r="K30">
+      <c r="K30" s="3">
         <v>23.4</v>
       </c>
-      <c r="M30">
+      <c r="M30" s="3">
         <v>0.9</v>
       </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
-      <c r="O30">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
         <v>0.9</v>
       </c>
-      <c r="P30" t="s">
+      <c r="P30" s="3" t="s">
         <v>2</v>
       </c>
       <c r="Q30" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="R30" s="6" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
+    <row r="31" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="3">
         <v>261</v>
       </c>
-      <c r="E31" t="s">
-        <v>1</v>
-      </c>
-      <c r="F31">
+      <c r="E31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="3">
         <v>261</v>
       </c>
-      <c r="G31" s="1">
-        <v>2</v>
-      </c>
-      <c r="H31">
+      <c r="G31" s="4">
+        <v>2</v>
+      </c>
+      <c r="H31" s="3">
         <v>2011</v>
       </c>
-      <c r="I31">
+      <c r="I31" s="3">
         <v>0.03</v>
       </c>
-      <c r="J31">
+      <c r="J31" s="3">
         <v>0.5</v>
       </c>
-      <c r="K31">
+      <c r="K31" s="3">
         <v>1.96</v>
       </c>
-      <c r="M31">
-        <v>0</v>
-      </c>
-      <c r="N31">
-        <v>0</v>
-      </c>
-      <c r="O31">
-        <v>0</v>
-      </c>
-      <c r="P31" t="s">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3" t="s">
         <v>2</v>
       </c>
       <c r="Q31" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="R31" s="6" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
+    <row r="32" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="3">
         <v>7</v>
       </c>
-      <c r="E32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F32">
+      <c r="E32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="3">
         <v>7</v>
       </c>
-      <c r="G32" s="1">
-        <v>1</v>
-      </c>
-      <c r="H32">
+      <c r="G32" s="4">
+        <v>1</v>
+      </c>
+      <c r="H32" s="3">
         <v>2012</v>
       </c>
-      <c r="I32">
+      <c r="I32" s="3">
         <v>0.04</v>
       </c>
-      <c r="J32">
+      <c r="J32" s="3">
         <v>0.1</v>
       </c>
-      <c r="K32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32">
-        <v>0</v>
-      </c>
-      <c r="P32" t="s">
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q32" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="R32" s="6" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
+    <row r="33" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="3">
         <v>587</v>
       </c>
-      <c r="E33" t="s">
-        <v>1</v>
-      </c>
-      <c r="F33">
+      <c r="E33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="3">
         <v>587</v>
       </c>
-      <c r="G33" s="1">
-        <v>1</v>
-      </c>
-      <c r="H33">
+      <c r="G33" s="4">
+        <v>1</v>
+      </c>
+      <c r="H33" s="3">
         <v>2012</v>
       </c>
-      <c r="I33">
+      <c r="I33" s="3">
         <v>0.04</v>
       </c>
-      <c r="J33">
+      <c r="J33" s="3">
         <v>0.5</v>
       </c>
-      <c r="K33">
+      <c r="K33" s="3">
         <v>5.9</v>
       </c>
-      <c r="M33">
+      <c r="M33" s="3">
         <v>0.6</v>
       </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
-      <c r="O33">
+      <c r="N33" s="3">
+        <v>0</v>
+      </c>
+      <c r="O33" s="3">
         <v>0.6</v>
       </c>
-      <c r="P33" t="s">
+      <c r="P33" s="3" t="s">
         <v>2</v>
       </c>
       <c r="Q33" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="R33" s="6" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
+    <row r="34" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="3">
         <v>243</v>
       </c>
-      <c r="E34" t="s">
-        <v>1</v>
-      </c>
-      <c r="F34">
+      <c r="E34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="3">
         <v>243</v>
       </c>
-      <c r="G34" s="1">
+      <c r="G34" s="4">
         <v>3</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="3">
         <v>2009</v>
       </c>
-      <c r="I34">
+      <c r="I34" s="3">
         <v>0.04</v>
       </c>
-      <c r="J34">
+      <c r="J34" s="3">
         <v>0.5</v>
       </c>
-      <c r="K34">
+      <c r="K34" s="3">
         <v>2.4</v>
       </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
-      <c r="N34">
-        <v>0</v>
-      </c>
-      <c r="O34">
-        <v>0</v>
-      </c>
-      <c r="P34" t="s">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3" t="s">
         <v>2</v>
       </c>
       <c r="Q34" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="R34" s="6" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>35</v>
       </c>
@@ -2708,88 +2774,94 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
+    <row r="36" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C36" t="s">
-        <v>1</v>
-      </c>
-      <c r="F36" t="s">
-        <v>1</v>
-      </c>
-      <c r="I36">
+      <c r="C36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="I36" s="3">
         <v>0.04</v>
       </c>
-      <c r="J36">
+      <c r="J36" s="3">
         <v>0.5</v>
       </c>
-      <c r="K36" t="s">
-        <v>1</v>
-      </c>
-      <c r="M36">
-        <v>0</v>
-      </c>
-      <c r="N36">
-        <v>0</v>
-      </c>
-      <c r="O36">
-        <v>0</v>
-      </c>
-      <c r="P36" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
+      <c r="K36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="M36" s="3">
+        <v>0</v>
+      </c>
+      <c r="N36" s="3">
+        <v>0</v>
+      </c>
+      <c r="O36" s="3">
+        <v>0</v>
+      </c>
+      <c r="P36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q36" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C37" s="1">
+      <c r="C37" s="4">
         <v>639545</v>
       </c>
-      <c r="D37" s="1"/>
-      <c r="E37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F37" s="1">
+      <c r="D37" s="4"/>
+      <c r="E37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="4">
         <v>541317</v>
       </c>
-      <c r="G37" s="1">
-        <v>1</v>
-      </c>
-      <c r="H37">
+      <c r="G37" s="4">
+        <v>1</v>
+      </c>
+      <c r="H37" s="3">
         <v>2011</v>
       </c>
-      <c r="I37">
+      <c r="I37" s="3">
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="J37">
+      <c r="J37" s="3">
         <v>0.5</v>
       </c>
-      <c r="K37" s="1">
+      <c r="K37" s="4">
         <v>11638</v>
       </c>
-      <c r="L37" s="1"/>
-      <c r="M37">
+      <c r="L37" s="4"/>
+      <c r="M37" s="3">
         <v>4.5999999999999996</v>
       </c>
-      <c r="N37">
+      <c r="N37" s="3">
         <v>463</v>
       </c>
-      <c r="O37">
+      <c r="O37" s="3">
         <v>471</v>
       </c>
-      <c r="P37" t="s">
+      <c r="P37" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q37" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>56</v>
       </c>
@@ -2834,162 +2906,174 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
+    <row r="39" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B39" t="s">
-        <v>0</v>
-      </c>
-      <c r="C39" s="1">
+      <c r="B39" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="4">
         <v>61100</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="F39" t="s">
-        <v>1</v>
-      </c>
-      <c r="G39">
-        <v>1</v>
-      </c>
-      <c r="H39">
+      <c r="F39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G39" s="3">
+        <v>1</v>
+      </c>
+      <c r="H39" s="3">
         <v>2012</v>
       </c>
-      <c r="I39">
+      <c r="I39" s="3">
         <v>0.12</v>
       </c>
-      <c r="J39">
+      <c r="J39" s="3">
         <v>0.5</v>
       </c>
-      <c r="K39" t="s">
-        <v>1</v>
-      </c>
-      <c r="M39">
+      <c r="K39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="M39" s="3">
         <v>1.02</v>
       </c>
-      <c r="N39">
+      <c r="N39" s="3">
         <v>193</v>
       </c>
-      <c r="O39">
+      <c r="O39" s="3">
         <v>194</v>
       </c>
-      <c r="P39" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
+      <c r="P39" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q39" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="3">
         <v>31</v>
       </c>
-      <c r="E40">
+      <c r="E40" s="3">
         <v>0.23</v>
       </c>
-      <c r="F40">
+      <c r="F40" s="3">
         <v>25.7</v>
       </c>
-      <c r="H40">
+      <c r="H40" s="3">
         <v>2010</v>
       </c>
-      <c r="I40">
+      <c r="I40" s="3">
         <v>0.04</v>
       </c>
-      <c r="J40">
+      <c r="J40" s="3">
         <v>0.1</v>
       </c>
-      <c r="K40">
-        <v>0</v>
-      </c>
-      <c r="M40">
-        <v>0</v>
-      </c>
-      <c r="N40">
-        <v>0</v>
-      </c>
-      <c r="O40">
-        <v>0</v>
-      </c>
-      <c r="P40" t="s">
+      <c r="K40" s="3">
+        <v>0</v>
+      </c>
+      <c r="M40" s="3">
+        <v>0</v>
+      </c>
+      <c r="N40" s="3">
+        <v>0</v>
+      </c>
+      <c r="O40" s="3">
+        <v>0</v>
+      </c>
+      <c r="P40" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
+      <c r="Q40" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B41" t="s">
-        <v>0</v>
-      </c>
-      <c r="C41" t="s">
-        <v>1</v>
-      </c>
-      <c r="F41" t="s">
-        <v>1</v>
-      </c>
-      <c r="I41">
+      <c r="B41" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="I41" s="3">
         <v>0.12</v>
       </c>
-      <c r="J41">
+      <c r="J41" s="3">
         <v>0.5</v>
       </c>
-      <c r="K41" t="s">
-        <v>1</v>
-      </c>
-      <c r="M41">
+      <c r="K41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="M41" s="3">
         <v>3.52</v>
       </c>
-      <c r="N41" s="1">
+      <c r="N41" s="4">
         <v>9567</v>
       </c>
-      <c r="O41" s="1">
+      <c r="O41" s="4">
         <v>9571</v>
       </c>
-      <c r="P41" t="s">
+      <c r="P41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
+      <c r="Q41" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C42" t="s">
-        <v>1</v>
-      </c>
-      <c r="F42" t="s">
-        <v>1</v>
-      </c>
-      <c r="I42">
+      <c r="C42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="I42" s="3">
         <v>0.04</v>
       </c>
-      <c r="J42">
+      <c r="J42" s="3">
         <v>0.1</v>
       </c>
-      <c r="K42" t="s">
-        <v>1</v>
-      </c>
-      <c r="M42">
+      <c r="K42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="M42" s="3">
         <v>0.28000000000000003</v>
       </c>
-      <c r="N42">
-        <v>0</v>
-      </c>
-      <c r="O42">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
         <v>0.28000000000000003</v>
       </c>
-      <c r="P42" t="s">
+      <c r="P42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -3024,130 +3108,139 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
+    <row r="44" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B44" t="s">
-        <v>0</v>
-      </c>
-      <c r="C44" t="s">
-        <v>1</v>
-      </c>
-      <c r="F44" t="s">
-        <v>1</v>
-      </c>
-      <c r="I44">
+      <c r="B44" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="I44" s="3">
         <v>0.04</v>
       </c>
-      <c r="J44">
+      <c r="J44" s="3">
         <v>0.5</v>
       </c>
-      <c r="K44" t="s">
-        <v>1</v>
-      </c>
-      <c r="M44">
-        <v>0</v>
-      </c>
-      <c r="N44">
-        <v>0</v>
-      </c>
-      <c r="O44">
-        <v>0</v>
-      </c>
-      <c r="P44" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
+      <c r="K44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="3">
         <f>AVERAGE(63160, 78198)</f>
         <v>70679</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="F45" s="1">
+      <c r="F45" s="4">
         <v>34485</v>
       </c>
-      <c r="G45" s="1">
-        <v>2</v>
-      </c>
-      <c r="H45">
+      <c r="G45" s="4">
+        <v>2</v>
+      </c>
+      <c r="H45" s="3">
         <v>2011</v>
       </c>
-      <c r="I45">
+      <c r="I45" s="3">
         <v>0.12</v>
       </c>
-      <c r="J45">
+      <c r="J45" s="3">
         <v>0.75</v>
       </c>
-      <c r="K45" s="1">
+      <c r="K45" s="4">
         <v>1552</v>
       </c>
-      <c r="L45" s="1"/>
-      <c r="M45">
+      <c r="L45" s="4"/>
+      <c r="M45" s="3">
         <v>49</v>
       </c>
-      <c r="N45">
+      <c r="N45" s="3">
         <v>11.9</v>
       </c>
-      <c r="O45">
+      <c r="O45" s="3">
         <v>65.099999999999994</v>
       </c>
-      <c r="P45" t="s">
+      <c r="P45" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q45" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="R45" s="6" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
+    <row r="46" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C46" s="1">
+      <c r="C46" s="4">
         <v>45659</v>
       </c>
-      <c r="D46" s="1"/>
-      <c r="F46" s="1">
+      <c r="D46" s="4"/>
+      <c r="F46" s="4">
         <v>45659</v>
       </c>
-      <c r="G46" s="1">
-        <v>1</v>
-      </c>
-      <c r="H46">
+      <c r="G46" s="4">
+        <v>1</v>
+      </c>
+      <c r="H46" s="3">
         <v>2012</v>
       </c>
-      <c r="I46">
+      <c r="I46" s="3">
         <v>0.12</v>
       </c>
-      <c r="J46">
+      <c r="J46" s="3">
         <v>0.1</v>
       </c>
-      <c r="K46">
+      <c r="K46" s="3">
         <v>274</v>
       </c>
-      <c r="M46">
+      <c r="M46" s="3">
         <v>29.6</v>
       </c>
-      <c r="N46">
+      <c r="N46" s="3">
         <v>199</v>
       </c>
-      <c r="O46">
+      <c r="O46" s="3">
         <v>230</v>
       </c>
-      <c r="P46" t="s">
+      <c r="P46" s="3" t="s">
         <v>4</v>
+      </c>
+      <c r="Q46" s="3" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
